--- a/data/trans_orig/dukeGLOBAL-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala global de apoyo funcional social (Duke)</t>
+          <t>Puntuación media de la escala global de apoyo funcional social (Duke) (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,94; 46,03</t>
+          <t>44,8; 45,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,52; 47,63</t>
+          <t>46,54; 47,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,2; 46,36</t>
+          <t>45,23; 46,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 46,15</t>
+          <t>44,6; 46,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,9; 44,92</t>
+          <t>43,81; 44,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,2; 47,05</t>
+          <t>46,14; 47,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,08; 45,22</t>
+          <t>44,13; 45,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,14; 45,29</t>
+          <t>44,18; 45,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,5; 45,28</t>
+          <t>44,49; 45,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,49; 47,16</t>
+          <t>46,49; 47,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,75; 45,55</t>
+          <t>44,75; 45,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,52; 45,5</t>
+          <t>44,55; 45,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,22; 48,9</t>
+          <t>48,25; 48,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 49,11</t>
+          <t>48,52; 49,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,53; 47,15</t>
+          <t>46,53; 47,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,52; 51,23</t>
+          <t>48,41; 51,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,22; 48,0</t>
+          <t>47,26; 48,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,38; 48,08</t>
+          <t>47,38; 48,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,49; 47,1</t>
+          <t>46,51; 47,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,06; 49,35</t>
+          <t>48,03; 49,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,87; 48,38</t>
+          <t>47,88; 48,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,08; 48,54</t>
+          <t>48,07; 48,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,58; 47,03</t>
+          <t>46,61; 47,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,4; 50,15</t>
+          <t>48,4; 50,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,0; 49,32</t>
+          <t>47,93; 49,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,75; 50,03</t>
+          <t>48,72; 50,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,11</t>
+          <t>48,08; 49,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,97; 50,17</t>
+          <t>48,95; 50,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,91; 49,37</t>
+          <t>47,96; 49,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,31; 50,39</t>
+          <t>49,33; 50,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,02; 49,11</t>
+          <t>48,05; 49,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,77; 50,61</t>
+          <t>49,76; 50,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,21; 49,15</t>
+          <t>48,14; 49,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 50,08</t>
+          <t>49,11; 50,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,16; 48,93</t>
+          <t>48,21; 48,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,5; 50,25</t>
+          <t>49,49; 50,27</t>
         </is>
       </c>
     </row>
@@ -1136,32 +1136,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,87</t>
+          <t>47,33; 47,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,17; 48,65</t>
+          <t>48,14; 48,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,67; 47,12</t>
+          <t>46,64; 47,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,18; 50,44</t>
+          <t>48,17; 50,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,21; 46,8</t>
+          <t>46,24; 46,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,34; 47,87</t>
+          <t>47,35; 47,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,74; 48,58</t>
+          <t>47,69; 48,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,84; 47,26</t>
+          <t>46,86; 47,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,82; 48,16</t>
+          <t>47,82; 48,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 46,85</t>
+          <t>46,49; 46,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,35</t>
+          <t>48,04; 49,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeGLOBAL-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/dukeGLOBAL-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45,41</t>
+          <t>45,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>44,74</t>
+          <t>44,54</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,01</t>
+          <t>44,79</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,8; 45,96</t>
+          <t>44,89; 46,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,54; 47,62</t>
+          <t>46,58; 47,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,23; 46,35</t>
+          <t>45,24; 46,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,6; 46,17</t>
+          <t>44,28; 45,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,81; 44,86</t>
+          <t>43,83; 44,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,14; 47,03</t>
+          <t>46,15; 47,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,13; 45,22</t>
+          <t>44,11; 45,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,18; 45,26</t>
+          <t>44,01; 45,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,49; 45,24</t>
+          <t>44,47; 45,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,49; 47,18</t>
+          <t>46,49; 47,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44,75; 45,54</t>
+          <t>44,77; 45,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,55; 45,44</t>
+          <t>44,33; 45,25</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,27</t>
+          <t>48,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,47</t>
+          <t>47,93</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,9</t>
+          <t>48,11</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,25; 48,9</t>
+          <t>48,23; 48,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,52; 49,13</t>
+          <t>48,46; 49,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,53; 47,12</t>
+          <t>46,54; 47,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,41; 51,04</t>
+          <t>47,9; 48,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,26; 48,04</t>
+          <t>47,21; 48,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,38; 48,1</t>
+          <t>47,42; 48,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,51; 47,13</t>
+          <t>46,52; 47,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,03; 49,19</t>
+          <t>47,62; 48,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,88; 48,37</t>
+          <t>47,87; 48,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48,07; 48,55</t>
+          <t>48,08; 48,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,4; 50,17</t>
+          <t>47,86; 48,34</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49,61</t>
+          <t>49,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,2</t>
+          <t>50,11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,91</t>
+          <t>49,84</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47,93; 49,29</t>
+          <t>48,03; 49,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,72; 50,06</t>
+          <t>48,72; 50,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,08; 49,16</t>
+          <t>48,05; 49,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,95; 50,2</t>
+          <t>48,88; 50,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,96; 49,31</t>
+          <t>47,95; 49,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,33; 50,4</t>
+          <t>49,27; 50,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,05; 49,13</t>
+          <t>48,0; 49,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,76; 50,62</t>
+          <t>49,64; 50,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,14; 49,12</t>
+          <t>48,18; 49,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,11; 50,07</t>
+          <t>49,24; 50,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,21; 48,96</t>
+          <t>48,22; 48,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,49; 50,27</t>
+          <t>49,46; 50,19</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48,76</t>
+          <t>48,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,19 +1103,19 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>47,63</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>47,06</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>48,0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47,06</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48,0</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
           <t>46,68</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,38</t>
+          <t>47,82</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,33; 47,89</t>
+          <t>47,31; 47,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,14; 48,66</t>
+          <t>48,17; 48,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,64; 47,1</t>
+          <t>46,66; 47,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,17; 50,38</t>
+          <t>47,73; 48,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,82</t>
+          <t>46,23; 46,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,35; 47,85</t>
+          <t>47,35; 47,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 46,73</t>
+          <t>46,24; 46,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,69; 48,56</t>
+          <t>47,38; 47,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,86; 47,25</t>
+          <t>46,84; 47,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,49; 46,86</t>
+          <t>46,51; 46,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,04; 49,17</t>
+          <t>47,6; 48,0</t>
         </is>
       </c>
     </row>
